--- a/diseases/d167/2020-2025.xlsx
+++ b/diseases/d167/2020-2025.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28521,7 +28521,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31272,7 +31272,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43062,7 +43062,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43455,7 +43455,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44241,7 +44241,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44634,7 +44634,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45027,7 +45027,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45813,7 +45813,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46206,7 +46206,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -57996,7 +57996,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58389,7 +58389,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -58782,7 +58782,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59175,7 +59175,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -59568,7 +59568,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -59961,7 +59961,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60354,7 +60354,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -60747,7 +60747,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -61140,7 +61140,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -61926,7 +61926,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -73861,7 +73861,7 @@
       </c>
       <c r="AM374" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN374" t="b">
@@ -74399,7 +74399,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -74937,7 +74937,7 @@
       </c>
       <c r="AM380" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN380" t="b">
@@ -75475,7 +75475,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -76013,7 +76013,7 @@
       </c>
       <c r="AM386" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN386" t="b">
@@ -76551,7 +76551,7 @@
       </c>
       <c r="AM389" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN389" t="b">
@@ -77089,7 +77089,7 @@
       </c>
       <c r="AM392" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN392" t="b">
@@ -77627,7 +77627,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -78165,7 +78165,7 @@
       </c>
       <c r="AM398" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN398" t="b">
@@ -78703,7 +78703,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -79241,7 +79241,7 @@
       </c>
       <c r="AM404" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN404" t="b">
@@ -79779,7 +79779,7 @@
       </c>
       <c r="AM407" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN407" t="b">
@@ -80317,7 +80317,7 @@
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -80855,7 +80855,7 @@
       </c>
       <c r="AM413" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN413" t="b">
@@ -81393,7 +81393,7 @@
       </c>
       <c r="AM416" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN416" t="b">
@@ -81931,7 +81931,7 @@
       </c>
       <c r="AM419" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN419" t="b">
@@ -82469,7 +82469,7 @@
       </c>
       <c r="AM422" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN422" t="b">
@@ -83007,7 +83007,7 @@
       </c>
       <c r="AM425" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN425" t="b">
@@ -83545,7 +83545,7 @@
       </c>
       <c r="AM428" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN428" t="b">
@@ -84083,7 +84083,7 @@
       </c>
       <c r="AM431" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN431" t="b">
@@ -84621,7 +84621,7 @@
       </c>
       <c r="AM434" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN434" t="b">
@@ -85159,7 +85159,7 @@
       </c>
       <c r="AM437" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN437" t="b">
@@ -85697,7 +85697,7 @@
       </c>
       <c r="AM440" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN440" t="b">

--- a/diseases/d167/2020-2025.xlsx
+++ b/diseases/d167/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28118,7 +28118,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30476,7 +30476,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31262,7 +31262,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43052,7 +43052,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43838,7 +43838,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -44624,7 +44624,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45410,7 +45410,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46982,7 +46982,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -57986,7 +57986,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -58379,7 +58379,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -58772,7 +58772,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59165,7 +59165,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -59558,7 +59558,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -59951,7 +59951,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60344,7 +60344,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60737,7 +60737,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61130,7 +61130,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -61523,7 +61523,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61916,7 +61916,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62309,7 +62309,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -73851,7 +73851,7 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
@@ -74389,7 +74389,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -74927,7 +74927,7 @@
       </c>
       <c r="AJ380" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK380" t="inlineStr">
@@ -75465,7 +75465,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -76003,7 +76003,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -76541,7 +76541,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -77079,7 +77079,7 @@
       </c>
       <c r="AJ392" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK392" t="inlineStr">
@@ -77617,7 +77617,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -78155,7 +78155,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -78693,7 +78693,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -79231,7 +79231,7 @@
       </c>
       <c r="AJ404" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK404" t="inlineStr">
@@ -79769,7 +79769,7 @@
       </c>
       <c r="AJ407" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK407" t="inlineStr">
@@ -80307,7 +80307,7 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
@@ -80845,7 +80845,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -81383,7 +81383,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -81921,7 +81921,7 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
@@ -82459,7 +82459,7 @@
       </c>
       <c r="AJ422" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK422" t="inlineStr">
@@ -82997,7 +82997,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -83535,7 +83535,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -84073,7 +84073,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -84611,7 +84611,7 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
@@ -85149,7 +85149,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -85687,7 +85687,7 @@
       </c>
       <c r="AJ440" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK440" t="inlineStr">
